--- a/reports/pdf_rolling5_20260914.xlsx
+++ b/reports/pdf_rolling5_20260914.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,659억   ·   현금 24억(0.5%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 11종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,523억   ·   현금 12억(0.3%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -839,88 +839,88 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>28</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>12536370000</v>
+        <v>892038000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>3.02%→5.75%</t>
+          <t>0.57%→0.75%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>30→58</t>
+          <t>78→106</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-10504260000</v>
+        <v>-1316952000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>5.77%→2.92%</t>
+          <t>1.12%→0.73%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>88→49</t>
+          <t>137→98</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>28</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>892038000</v>
+        <v>12536370000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.75%</t>
+          <t>3.02%→5.75%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>78→106</t>
+          <t>30→58</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1316952000</v>
+        <v>-10504260000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.73%</t>
+          <t>5.77%→2.92%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>137→98</t>
+          <t>88→49</t>
         </is>
       </c>
     </row>
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-760986000</v>
+        <v>-797166000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.09%→0.81%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1152,23 +1152,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-797166000</v>
+        <v>-760986000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,489억   ·   현금 87억(2.5%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,429억   ·   현금 43억(1.3%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1283,7 +1283,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 79억(3.1%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 9종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,549억   ·   현금 40억(1.6%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 9종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1379,7 +1379,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>506456400</v>
+        <v>504982000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>-224</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1548113280</v>
+        <v>-1543606400</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>77</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2584116150</v>
+        <v>2576593250</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>-150</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2066152500</v>
+        <v>-2060137500</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>60</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>3990096000</v>
+        <v>3978480000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>-105</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1554509250</v>
+        <v>-1549983750</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>25</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>5556112500</v>
+        <v>5539937500</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>-99</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1401067800</v>
+        <v>-1396989000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>23</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2267443500</v>
+        <v>2260842500</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>-96</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-8652902400</v>
+        <v>-8627712000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>596041200</v>
+        <v>594306000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>-65</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-2002776750</v>
+        <v>-1996946250</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>15</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2684452500</v>
+        <v>2676637500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>-63</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2053683450</v>
+        <v>-2047704750</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>498762000</v>
+        <v>497310000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>-50</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1659105000</v>
+        <v>-1654275000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1530292500</v>
+        <v>1525837500</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>-30</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-693526500</v>
+        <v>-691507500</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,974억   ·   현금 36억(1.8%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 6종목  /  매도 7종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,944억   ·   현금 18억(0.9%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 6종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -2149,7 +2149,7 @@
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 2억(0.6%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 5종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 1억(0.3%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 5종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B49" s="4" t="n"/>
@@ -2245,11 +2245,11 @@
         <v>274</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>189882000</v>
+        <v>192375400</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>6.69%→7.34%</t>
+          <t>6.90%→7.58%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2266,11 +2266,11 @@
         <v>-40</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-65240000</v>
+        <v>-67200000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>5.29%→5.04%</t>
+          <t>5.55%→5.29%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2289,11 +2289,11 @@
         <v>39</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>186186000</v>
+        <v>180180000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.32%→0.98%</t>
+          <t>0.32%→0.97%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2310,11 +2310,11 @@
         <v>-37</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-126651000</v>
+        <v>-126521500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>4.37%→3.91%</t>
+          <t>4.45%→3.98%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2333,11 +2333,11 @@
         <v>27</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>82309500</v>
+        <v>82215000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.09%→1.38%</t>
+          <t>1.11%→1.40%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2354,11 +2354,11 @@
         <v>-13</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-29484000</v>
+        <v>-28847000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>2.12%→2.01%</t>
+          <t>2.11%→2.00%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2377,11 +2377,11 @@
         <v>26</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>38675000</v>
+        <v>37856000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>1.55%→1.69%</t>
+          <t>1.55%→1.68%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2398,11 +2398,11 @@
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-22270500</v>
+        <v>-25105500</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.90%</t>
+          <t>1.13%→1.03%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2421,11 +2421,11 @@
         <v>4</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>24360000</v>
+        <v>23800000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>1.72%→1.80%</t>
+          <t>1.71%→1.79%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2442,11 +2442,11 @@
         <v>-8</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-86800000</v>
+        <v>-87920000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.75%→3.43%</t>
+          <t>3.87%→3.55%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2470,11 +2470,11 @@
         <v>-7</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-58212000</v>
+        <v>-54047000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.52%→2.31%</t>
+          <t>2.38%→2.18%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2498,11 +2498,11 @@
         <v>-5</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-66710000</v>
+        <v>-66570000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.81%→1.57%</t>
+          <t>1.84%→1.59%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 493억   ·   현금 9억(1.8%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 485억   ·   현금 4억(0.9%)      오늘 2026-09-14  vs  5일전 2026-09-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260914.xlsx
+++ b/reports/pdf_rolling5_20260914.xlsx
@@ -839,88 +839,88 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>28</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>892038000</v>
+        <v>12536370000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.75%</t>
+          <t>3.02%→5.75%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>78→106</t>
+          <t>30→58</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1316952000</v>
+        <v>-10504260000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.73%</t>
+          <t>5.77%→2.92%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>137→98</t>
+          <t>88→49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>28</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>12536370000</v>
+        <v>892038000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>3.02%→5.75%</t>
+          <t>0.57%→0.75%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>30→58</t>
+          <t>78→106</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-10504260000</v>
+        <v>-1316952000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>5.77%→2.92%</t>
+          <t>1.12%→0.73%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>88→49</t>
+          <t>137→98</t>
         </is>
       </c>
     </row>
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-797166000</v>
+        <v>-760986000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1152,23 +1152,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-760986000</v>
+        <v>-797166000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.09%→0.81%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260914.xlsx
+++ b/reports/pdf_rolling5_20260914.xlsx
@@ -839,88 +839,88 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>28</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>12536370000</v>
+        <v>892038000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>3.02%→5.75%</t>
+          <t>0.57%→0.75%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>30→58</t>
+          <t>78→106</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-10504260000</v>
+        <v>-1316952000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>5.77%→2.92%</t>
+          <t>1.12%→0.73%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>88→49</t>
+          <t>137→98</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>28</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>892038000</v>
+        <v>12536370000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.75%</t>
+          <t>3.02%→5.75%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>78→106</t>
+          <t>30→58</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-39</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1316952000</v>
+        <v>-10504260000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.73%</t>
+          <t>5.77%→2.92%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>137→98</t>
+          <t>88→49</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260914.xlsx
+++ b/reports/pdf_rolling5_20260914.xlsx
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-760986000</v>
+        <v>-797166000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.09%→0.81%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1152,23 +1152,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-797166000</v>
+        <v>-760986000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
